--- a/Fourth Semester/static and probability/lab3/lab3.xlsx
+++ b/Fourth Semester/static and probability/lab3/lab3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER-WIN10\Documents\GitHub\BCE\Fourth Semester\static and probability\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E7B312-5E3D-4654-875C-4A9F8A743D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D44F234-FBEE-421F-B168-E80054DB1000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Fourth Semester/static and probability/lab3/lab3.xlsx
+++ b/Fourth Semester/static and probability/lab3/lab3.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER-WIN10\Documents\GitHub\BCE\Fourth Semester\static and probability\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D44F234-FBEE-421F-B168-E80054DB1000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FB328D-D7EE-4825-9226-2530E74027FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3(assign)" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4(assign)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>Daily Rainfall</t>
   </si>
@@ -131,13 +131,45 @@
   <si>
     <t>N</t>
   </si>
+  <si>
+    <t xml:space="preserve"> =SUM(B19:B42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =SUM(C19:C42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =SUM(D19:D42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =SUM(E19:E42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =SUM(F19:F42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =COUNT(B19:B42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =(C47*F43-B43*C43)/((SQRT(C47*D43-B43^2))*(SQRT(C47*E43-C43^2)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =CORREL(B19:B42,C19:C42)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -165,8 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,7 +667,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet3!$B$1</c:f>
+              <c:f>'Sheet3(assign)'!$B$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -667,7 +700,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet3!$A$2:$A$25</c:f>
+              <c:f>'Sheet3(assign)'!$A$19:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -748,7 +781,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet3!$B$2:$B$25</c:f>
+              <c:f>'Sheet3(assign)'!$B$19:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2283,13 +2316,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>157162</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>42862</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2977,210 +3010,210 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A18:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B18" s="1" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>24</v>
-      </c>
-      <c r="B2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>22</v>
-      </c>
-      <c r="B3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>35</v>
-      </c>
-      <c r="B4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>35</v>
-      </c>
-      <c r="B5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>31</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>33</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>33</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>21</v>
-      </c>
-      <c r="B10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>30</v>
-      </c>
-      <c r="B11">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>25</v>
-      </c>
-      <c r="B13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>34</v>
-      </c>
-      <c r="B16">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>33</v>
-      </c>
-      <c r="B17">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>33</v>
-      </c>
-      <c r="B18">
-        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
+        <v>33</v>
+      </c>
+      <c r="B25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>30</v>
+      </c>
+      <c r="B28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>25</v>
+      </c>
+      <c r="B30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="B32">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>34</v>
+      </c>
+      <c r="B33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>19</v>
       </c>
-      <c r="B25">
+      <c r="B37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>32</v>
+      </c>
+      <c r="B38">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>21</v>
+      </c>
+      <c r="B39">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>35</v>
+      </c>
+      <c r="B40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>27</v>
+      </c>
+      <c r="B41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>19</v>
+      </c>
+      <c r="B42">
         <v>19</v>
       </c>
     </row>
@@ -3192,588 +3225,612 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A18:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>24</v>
       </c>
-      <c r="C2">
+      <c r="C19">
         <v>23</v>
       </c>
-      <c r="D2">
-        <f>B2^2</f>
+      <c r="D19">
+        <f>B19^2</f>
         <v>576</v>
       </c>
-      <c r="E2">
-        <f>C2^2</f>
+      <c r="E19">
+        <f>C19^2</f>
         <v>529</v>
       </c>
-      <c r="F2">
-        <f>B2*C2</f>
+      <c r="F19">
+        <f>B19*C19</f>
         <v>552</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20">
         <v>22</v>
       </c>
-      <c r="C3">
+      <c r="C20">
         <v>20</v>
       </c>
-      <c r="D3">
-        <f>B3^2</f>
+      <c r="D20">
+        <f>B20^2</f>
         <v>484</v>
       </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E24" si="0">C3^2</f>
+      <c r="E20">
+        <f t="shared" ref="E20:E41" si="0">C20^2</f>
         <v>400</v>
       </c>
-      <c r="F3">
-        <f>B3*C3</f>
+      <c r="F20">
+        <f>B20*C20</f>
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>35</v>
       </c>
-      <c r="C4">
+      <c r="C21">
         <v>30</v>
       </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D24" si="1">B4^2</f>
+      <c r="D21">
+        <f t="shared" ref="D21:D41" si="1">B21^2</f>
         <v>1225</v>
       </c>
-      <c r="E4">
+      <c r="E21">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F24" si="2">B4*C4</f>
+      <c r="F21">
+        <f t="shared" ref="F21:F41" si="2">B21*C21</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>35</v>
       </c>
-      <c r="C5">
+      <c r="C22">
         <v>28</v>
       </c>
-      <c r="D5">
+      <c r="D22">
         <f t="shared" si="1"/>
         <v>1225</v>
       </c>
-      <c r="E5">
+      <c r="E22">
         <f t="shared" si="0"/>
         <v>784</v>
       </c>
-      <c r="F5">
+      <c r="F22">
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>23</v>
       </c>
-      <c r="C6">
+      <c r="C23">
         <v>20</v>
       </c>
-      <c r="D6">
+      <c r="D23">
         <f t="shared" si="1"/>
         <v>529</v>
       </c>
-      <c r="E6">
+      <c r="E23">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="F6">
+      <c r="F23">
         <f t="shared" si="2"/>
         <v>460</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C24">
         <v>26</v>
       </c>
-      <c r="D7">
+      <c r="D24">
         <f t="shared" si="1"/>
         <v>961</v>
       </c>
-      <c r="E7">
+      <c r="E24">
         <f t="shared" si="0"/>
         <v>676</v>
       </c>
-      <c r="F7">
+      <c r="F24">
         <f t="shared" si="2"/>
         <v>806</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>33</v>
       </c>
-      <c r="C8">
+      <c r="C25">
         <v>23</v>
       </c>
-      <c r="D8">
+      <c r="D25">
         <f t="shared" si="1"/>
         <v>1089</v>
       </c>
-      <c r="E8">
+      <c r="E25">
         <f t="shared" si="0"/>
         <v>529</v>
       </c>
-      <c r="F8">
+      <c r="F25">
         <f t="shared" si="2"/>
         <v>759</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C26">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="D26">
         <f t="shared" si="1"/>
         <v>1089</v>
       </c>
-      <c r="E9">
+      <c r="E26">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="F9">
+      <c r="F26">
         <f t="shared" si="2"/>
         <v>660</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27">
         <v>21</v>
       </c>
-      <c r="C10">
+      <c r="C27">
         <v>21</v>
       </c>
-      <c r="D10">
+      <c r="D27">
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="E10">
+      <c r="E27">
         <f t="shared" si="0"/>
         <v>441</v>
       </c>
-      <c r="F10">
+      <c r="F27">
         <f t="shared" si="2"/>
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28">
         <v>30</v>
       </c>
-      <c r="C11">
+      <c r="C28">
         <v>30</v>
       </c>
-      <c r="D11">
+      <c r="D28">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="E11">
+      <c r="E28">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="F11">
+      <c r="F28">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29">
         <v>27</v>
       </c>
-      <c r="C12">
+      <c r="C29">
         <v>27</v>
       </c>
-      <c r="D12">
+      <c r="D29">
         <f t="shared" si="1"/>
         <v>729</v>
       </c>
-      <c r="E12">
+      <c r="E29">
         <f t="shared" si="0"/>
         <v>729</v>
       </c>
-      <c r="F12">
+      <c r="F29">
         <f t="shared" si="2"/>
         <v>729</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30">
         <v>25</v>
       </c>
-      <c r="C13">
+      <c r="C30">
         <v>20</v>
       </c>
-      <c r="D13">
+      <c r="D30">
         <f t="shared" si="1"/>
         <v>625</v>
       </c>
-      <c r="E13">
+      <c r="E30">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="F13">
+      <c r="F30">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31">
         <v>25</v>
       </c>
-      <c r="C14">
+      <c r="C31">
         <v>20</v>
       </c>
-      <c r="D14">
+      <c r="D31">
         <f t="shared" si="1"/>
         <v>625</v>
       </c>
-      <c r="E14">
+      <c r="E31">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="F14">
+      <c r="F31">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32">
         <v>24</v>
       </c>
-      <c r="C15">
+      <c r="C32">
         <v>23</v>
       </c>
-      <c r="D15">
+      <c r="D32">
         <f t="shared" si="1"/>
         <v>576</v>
       </c>
-      <c r="E15">
+      <c r="E32">
         <f t="shared" si="0"/>
         <v>529</v>
       </c>
-      <c r="F15">
+      <c r="F32">
         <f t="shared" si="2"/>
         <v>552</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33">
         <v>34</v>
       </c>
-      <c r="C16">
+      <c r="C33">
         <v>25</v>
       </c>
-      <c r="D16">
+      <c r="D33">
         <f t="shared" si="1"/>
         <v>1156</v>
       </c>
-      <c r="E16">
+      <c r="E33">
         <f t="shared" si="0"/>
         <v>625</v>
       </c>
-      <c r="F16">
+      <c r="F33">
         <f t="shared" si="2"/>
         <v>850</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B17">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34">
         <v>33</v>
       </c>
-      <c r="C17">
+      <c r="C34">
         <v>23</v>
       </c>
-      <c r="D17">
+      <c r="D34">
         <f t="shared" si="1"/>
         <v>1089</v>
       </c>
-      <c r="E17">
+      <c r="E34">
         <f t="shared" si="0"/>
         <v>529</v>
       </c>
-      <c r="F17">
+      <c r="F34">
         <f t="shared" si="2"/>
         <v>759</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B35">
         <v>33</v>
       </c>
-      <c r="C18">
+      <c r="C35">
         <v>27</v>
       </c>
-      <c r="D18">
+      <c r="D35">
         <f t="shared" si="1"/>
         <v>1089</v>
       </c>
-      <c r="E18">
+      <c r="E35">
         <f t="shared" si="0"/>
         <v>729</v>
       </c>
-      <c r="F18">
+      <c r="F35">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36">
         <v>30</v>
       </c>
-      <c r="C19">
+      <c r="C36">
         <v>27</v>
       </c>
-      <c r="D19">
+      <c r="D36">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="E19">
+      <c r="E36">
         <f t="shared" si="0"/>
         <v>729</v>
       </c>
-      <c r="F19">
+      <c r="F36">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37">
         <v>19</v>
       </c>
-      <c r="C20">
+      <c r="C37">
         <v>19</v>
       </c>
-      <c r="D20">
+      <c r="D37">
         <f t="shared" si="1"/>
         <v>361</v>
       </c>
-      <c r="E20">
+      <c r="E37">
         <f t="shared" si="0"/>
         <v>361</v>
       </c>
-      <c r="F20">
+      <c r="F37">
         <f t="shared" si="2"/>
         <v>361</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38">
         <v>32</v>
       </c>
-      <c r="C21">
+      <c r="C38">
         <v>19</v>
       </c>
-      <c r="D21">
+      <c r="D38">
         <f t="shared" si="1"/>
         <v>1024</v>
       </c>
-      <c r="E21">
+      <c r="E38">
         <f t="shared" si="0"/>
         <v>361</v>
       </c>
-      <c r="F21">
+      <c r="F38">
         <f t="shared" si="2"/>
         <v>608</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B39">
         <v>21</v>
       </c>
-      <c r="C22">
+      <c r="C39">
         <v>18</v>
       </c>
-      <c r="D22">
+      <c r="D39">
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="E22">
+      <c r="E39">
         <f t="shared" si="0"/>
         <v>324</v>
       </c>
-      <c r="F22">
+      <c r="F39">
         <f t="shared" si="2"/>
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40">
         <v>35</v>
       </c>
-      <c r="C23">
+      <c r="C40">
         <v>23</v>
       </c>
-      <c r="D23">
+      <c r="D40">
         <f t="shared" si="1"/>
         <v>1225</v>
       </c>
-      <c r="E23">
+      <c r="E40">
         <f t="shared" si="0"/>
         <v>529</v>
       </c>
-      <c r="F23">
+      <c r="F40">
         <f t="shared" si="2"/>
         <v>805</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41">
         <v>27</v>
       </c>
-      <c r="C24">
+      <c r="C41">
         <v>22</v>
       </c>
-      <c r="D24">
+      <c r="D41">
         <f t="shared" si="1"/>
         <v>729</v>
       </c>
-      <c r="E24">
+      <c r="E41">
         <f t="shared" si="0"/>
         <v>484</v>
       </c>
-      <c r="F24">
+      <c r="F41">
         <f t="shared" si="2"/>
         <v>594</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42">
         <v>19</v>
       </c>
-      <c r="C25">
+      <c r="C42">
         <v>19</v>
       </c>
-      <c r="D25">
-        <f>B25^2</f>
+      <c r="D42">
+        <f>B42^2</f>
         <v>361</v>
       </c>
-      <c r="E25">
-        <f>C25^2</f>
+      <c r="E42">
+        <f>C42^2</f>
         <v>361</v>
       </c>
-      <c r="F25">
-        <f>B25*C25</f>
+      <c r="F42">
+        <f>B42*C42</f>
         <v>361</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B26">
-        <f>SUM(B2:B25)</f>
+      <c r="B43">
+        <f>SUM(B19:B42)</f>
         <v>671</v>
       </c>
-      <c r="C26">
-        <f>SUM(C2:C25)</f>
+      <c r="C43">
+        <f>SUM(C19:C42)</f>
         <v>553</v>
       </c>
-      <c r="D26">
-        <f>SUM(D2:D25)</f>
+      <c r="D43">
+        <f>SUM(D19:D42)</f>
         <v>19449</v>
       </c>
-      <c r="E26">
-        <f>SUM(E2:E25)</f>
+      <c r="E43">
+        <f>SUM(E19:E42)</f>
         <v>13049</v>
       </c>
-      <c r="F26">
-        <f>SUM(F2:F25)</f>
+      <c r="F43">
+        <f>SUM(F19:F42)</f>
         <v>15746</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C46" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D46" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B47" t="s">
         <v>30</v>
       </c>
-      <c r="C30">
-        <f>COUNT(B2:B25)</f>
+      <c r="C47">
+        <f>COUNT(B19:B42)</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C32">
-        <f>(C30*F26-B26*C26)/((SQRT(C30*D26-B26^2))*(SQRT(C30*E26-C26^2)))</f>
+      <c r="C49">
+        <f>(C47*F43-B43*C43)/((SQRT(C47*D43-B43^2))*(SQRT(C47*E43-C43^2)))</f>
         <v>0.61982937694778939</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="D49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B51" t="s">
         <v>16</v>
       </c>
-      <c r="C34">
-        <f>CORREL(B2:B25,C2:C25)</f>
+      <c r="C51">
+        <f>CORREL(B19:B42,C19:C42)</f>
         <v>0.61982937694778928</v>
+      </c>
+      <c r="D51" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
